--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976DB2B8-DC94-46E5-92F0-3A6E241837B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6975D90-B59D-4D67-9B99-3DA9DE80D7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -100,12 +100,6 @@
     <t>bioenergy</t>
   </si>
   <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
     <t>hydrogen</t>
   </si>
   <si>
@@ -121,9 +115,6 @@
     <t>solar</t>
   </si>
   <si>
-    <t>oil</t>
-  </si>
-  <si>
     <t>ELC</t>
   </si>
   <si>
@@ -670,13 +661,19 @@
     <t>windoff</t>
   </si>
   <si>
-    <t>NRG, GAS</t>
-  </si>
-  <si>
     <t>wind onshore</t>
   </si>
   <si>
     <t>wind offshore</t>
+  </si>
+  <si>
+    <t>COAL</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>OIL</t>
   </si>
   <si>
     <t>IND</t>
@@ -3094,21 +3091,21 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
         <v>39</v>
-      </c>
-      <c r="H4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="F5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3177,7 +3174,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3209,19 +3206,19 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
+        <v>214</v>
+      </c>
+      <c r="O5" t="s">
         <v>215</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" t="s">
         <v>216</v>
-      </c>
-      <c r="P5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3229,7 +3226,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -3238,27 +3235,27 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
+        <v>217</v>
+      </c>
+      <c r="O6" t="s">
         <v>218</v>
       </c>
-      <c r="O6" t="s">
-        <v>219</v>
-      </c>
       <c r="P6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>210</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -3267,19 +3264,19 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" t="s">
         <v>220</v>
       </c>
-      <c r="O7" t="s">
-        <v>221</v>
-      </c>
       <c r="P7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3287,7 +3284,7 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -3298,7 +3295,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -3309,7 +3306,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
@@ -3320,7 +3317,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -3331,7 +3328,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -3342,7 +3339,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
@@ -3353,10 +3350,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -3367,10 +3364,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -3381,33 +3378,33 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -3415,13 +3412,13 @@
     </row>
     <row r="18" spans="2:7">
       <c r="B18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -3429,13 +3426,13 @@
     </row>
     <row r="19" spans="2:7">
       <c r="B19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
@@ -3443,13 +3440,13 @@
     </row>
     <row r="20" spans="2:7">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -3460,55 +3457,55 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" t="s">
         <v>196</v>
-      </c>
-      <c r="C22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="E23" t="s">
         <v>196</v>
-      </c>
-      <c r="C23" t="s">
-        <v>203</v>
-      </c>
-      <c r="E23" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" t="s">
         <v>196</v>
-      </c>
-      <c r="C24" t="s">
-        <v>204</v>
-      </c>
-      <c r="E24" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3535,7 +3532,7 @@
   <sheetData>
     <row r="3" spans="2:7">
       <c r="B3" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -3545,28 +3542,28 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14.25">
       <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="E12" s="8" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
@@ -3586,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14.25">
@@ -3594,7 +3591,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" ref="E14:G14" si="1">$B$4</f>
@@ -3614,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" s="6">
         <f>E14+3</f>
@@ -3634,7 +3631,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E16" s="6">
         <f>E15+5</f>
@@ -3654,7 +3651,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
@@ -3674,7 +3671,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="2"/>
@@ -3694,7 +3691,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="2"/>
@@ -3710,7 +3707,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="2"/>
@@ -3722,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="14.25">
@@ -3730,7 +3727,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.25">
@@ -3738,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="14.25">
@@ -3746,37 +3743,37 @@
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14.25">
@@ -3845,7 +3842,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -3853,42 +3850,42 @@
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="H5" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="I5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="K5" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="L5" s="15" t="s">
         <v>59</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="D6" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E6" s="11">
         <v>0</v>
@@ -3899,7 +3896,7 @@
     </row>
     <row r="7" spans="2:12">
       <c r="D7" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E7" s="11">
         <v>0</v>
@@ -3910,7 +3907,7 @@
     </row>
     <row r="8" spans="2:12">
       <c r="D8" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8" s="11">
         <v>0</v>
@@ -3921,7 +3918,7 @@
     </row>
     <row r="9" spans="2:12">
       <c r="D9" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E9" s="11">
         <v>0</v>
@@ -3932,7 +3929,7 @@
     </row>
     <row r="10" spans="2:12">
       <c r="D10" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E10" s="11">
         <v>0</v>
@@ -3943,7 +3940,7 @@
     </row>
     <row r="13" spans="2:12">
       <c r="B13" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
@@ -3951,50 +3948,50 @@
     </row>
     <row r="14" spans="2:12">
       <c r="B14" s="15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="15" t="s">
+      <c r="G14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:12">
       <c r="D15" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F15" s="11">
         <v>2222</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
       <c r="D16" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F16" s="11">
         <v>8888</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="12.75">
@@ -4391,13 +4388,13 @@
     <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -4405,56 +4402,56 @@
     <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I3" s="4">
         <v>2022</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="13.15">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I4" s="11">
         <v>0.05</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N4" s="6">
         <v>1055.55</v>
@@ -4463,25 +4460,25 @@
     <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I5" s="11">
         <v>1</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N5" s="6">
         <v>3.6</v>
@@ -4490,19 +4487,19 @@
     <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I6" s="11">
         <v>2025</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N6" s="6">
         <v>1000</v>
@@ -4511,19 +4508,19 @@
     <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I7" s="11">
         <v>1</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N7" s="6">
         <v>1000</v>
@@ -4532,25 +4529,25 @@
     <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I8" s="11">
         <v>2.2201</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N8" s="6">
         <v>1.05555</v>
@@ -4559,25 +4556,25 @@
     <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I9" s="11">
         <v>2.1427</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N9" s="6">
         <v>4.1868000000000002E-2</v>
@@ -4586,25 +4583,25 @@
     <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I10" s="11">
         <v>2.077</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N10" s="6">
         <v>41.868000000000002</v>
@@ -4613,25 +4610,25 @@
     <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I11" s="11">
         <v>2.0358000000000001</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N11" s="6">
         <v>3.5999999999999999E-3</v>
@@ -4640,25 +4637,25 @@
     <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I12" s="11">
         <v>1.9870000000000001</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N12" s="6">
         <v>1000000</v>
@@ -4667,25 +4664,25 @@
     <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I13" s="11">
         <v>1.9192</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N13" s="6">
         <v>1000</v>
@@ -4694,25 +4691,25 @@
     <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I14" s="11">
         <v>1.8468</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N14" s="6">
         <v>5.8615199999999996</v>
@@ -4721,25 +4718,25 @@
     <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I15" s="11">
         <v>1.7799</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N15" s="6">
         <v>1E-3</v>
@@ -4748,25 +4745,25 @@
     <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I16" s="11">
         <v>1.722</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N16" s="6">
         <v>1000</v>
@@ -4775,25 +4772,25 @@
     <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I17" s="11">
         <v>1.6836</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N17" s="6">
         <v>37.68</v>
@@ -4801,25 +4798,25 @@
     </row>
     <row r="18" spans="1:14" ht="13.15">
       <c r="B18" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I18" s="11">
         <v>1.6446000000000001</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N18" s="6">
         <v>2139.4548</v>
@@ -4827,25 +4824,25 @@
     </row>
     <row r="19" spans="1:14" ht="13.15">
       <c r="B19" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I19" s="11">
         <v>1.6102000000000001</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N19" s="6">
         <v>2.78</v>
@@ -4853,25 +4850,25 @@
     </row>
     <row r="20" spans="1:14" ht="13.15">
       <c r="B20" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I20" s="11">
         <v>1.5770999999999999</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N20" s="6">
         <v>3.6</v>
@@ -4879,25 +4876,25 @@
     </row>
     <row r="21" spans="1:14" ht="13.15">
       <c r="B21" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I21" s="11">
         <v>1.5488</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
@@ -4905,25 +4902,25 @@
     </row>
     <row r="22" spans="1:14" ht="13.15">
       <c r="B22" s="19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I22" s="11">
         <v>1.5224</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N22" s="6">
         <v>31.536000000000001</v>
@@ -4931,25 +4928,25 @@
     </row>
     <row r="23" spans="1:14" ht="13.15">
       <c r="B23" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I23" s="11">
         <v>1.5058</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N23" s="6">
         <v>120</v>
@@ -4957,25 +4954,25 @@
     </row>
     <row r="24" spans="1:14" ht="13.15">
       <c r="B24" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I24" s="11">
         <v>1.4844999999999999</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N24" s="11">
         <v>5.8615199999999996</v>
@@ -4983,25 +4980,25 @@
     </row>
     <row r="25" spans="1:14" ht="13.15">
       <c r="B25" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I25" s="11">
         <v>1.4518</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N25" s="11">
         <v>54</v>
@@ -5009,16 +5006,16 @@
     </row>
     <row r="26" spans="1:14" ht="13.15">
       <c r="B26" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I26" s="11">
         <v>1.4198999999999999</v>
@@ -5026,16 +5023,16 @@
     </row>
     <row r="27" spans="1:14" ht="13.15">
       <c r="B27" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I27" s="11">
         <v>1.3986000000000001</v>
@@ -5043,16 +5040,16 @@
     </row>
     <row r="28" spans="1:14" ht="13.15">
       <c r="B28" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I28" s="11">
         <v>1.3727</v>
@@ -5060,16 +5057,16 @@
     </row>
     <row r="29" spans="1:14" ht="13.15">
       <c r="B29" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="H29" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I29" s="11">
         <v>1.3369</v>
@@ -5077,16 +5074,16 @@
     </row>
     <row r="30" spans="1:14" ht="13.15">
       <c r="B30" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I30" s="11">
         <v>1.2967</v>
@@ -5094,16 +5091,16 @@
     </row>
     <row r="31" spans="1:14" ht="13.15">
       <c r="B31" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I31" s="11">
         <v>1.2583</v>
@@ -5111,16 +5108,16 @@
     </row>
     <row r="32" spans="1:14" ht="13.15">
       <c r="B32" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I32" s="11">
         <v>1.2253000000000001</v>
@@ -5128,16 +5125,16 @@
     </row>
     <row r="33" spans="2:9" ht="13.15">
       <c r="B33" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I33" s="11">
         <v>1.2023999999999999</v>
@@ -5145,16 +5142,16 @@
     </row>
     <row r="34" spans="2:9" ht="13.15">
       <c r="B34" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I34" s="11">
         <v>1.1931</v>
@@ -5162,16 +5159,16 @@
     </row>
     <row r="35" spans="2:9" ht="13.15">
       <c r="B35" s="19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I35" s="11">
         <v>1.1793</v>
@@ -5179,16 +5176,16 @@
     </row>
     <row r="36" spans="2:9" ht="13.15">
       <c r="B36" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I36" s="11">
         <v>1.1552</v>
@@ -5196,16 +5193,16 @@
     </row>
     <row r="37" spans="2:9" ht="13.15">
       <c r="B37" s="19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I37" s="11">
         <v>1.1334</v>
@@ -5213,16 +5210,16 @@
     </row>
     <row r="38" spans="2:9" ht="13.15">
       <c r="B38" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I38" s="11">
         <v>1.1136999999999999</v>
@@ -5230,16 +5227,16 @@
     </row>
     <row r="39" spans="2:9" ht="13.15">
       <c r="B39" s="19" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I39" s="11">
         <v>1.0934999999999999</v>
@@ -5247,16 +5244,16 @@
     </row>
     <row r="40" spans="2:9" ht="13.15">
       <c r="B40" s="19" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I40" s="11">
         <v>1.0831</v>
@@ -5264,16 +5261,16 @@
     </row>
     <row r="41" spans="2:9" ht="13.15">
       <c r="B41" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I41" s="11">
         <v>1.0719000000000001</v>
@@ -5281,16 +5278,16 @@
     </row>
     <row r="42" spans="2:9" ht="13.15">
       <c r="B42" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I42" s="11">
         <v>1.0519000000000001</v>
@@ -5298,16 +5295,16 @@
     </row>
     <row r="43" spans="2:9" ht="13.15">
       <c r="B43" s="19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I43" s="11">
         <v>1.0274000000000001</v>
@@ -5315,16 +5312,16 @@
     </row>
     <row r="44" spans="2:9" ht="13.15">
       <c r="B44" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I44" s="11">
         <v>1.0091000000000001</v>
@@ -5332,16 +5329,16 @@
     </row>
     <row r="45" spans="2:9" ht="13.15">
       <c r="B45" s="19" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I45" s="11">
         <v>1</v>
@@ -5349,16 +5346,16 @@
     </row>
     <row r="46" spans="2:9" ht="13.15">
       <c r="B46" s="19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I46" s="11">
         <v>0.98960000000000004</v>
@@ -5366,16 +5363,16 @@
     </row>
     <row r="47" spans="2:9" ht="13.15">
       <c r="B47" s="19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I47" s="11">
         <v>0.97809999999999997</v>
@@ -5383,16 +5380,16 @@
     </row>
     <row r="48" spans="2:9" ht="13.15">
       <c r="B48" s="19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I48" s="11">
         <v>0.96499999999999997</v>
@@ -5400,16 +5397,16 @@
     </row>
     <row r="49" spans="2:9" ht="13.15">
       <c r="B49" s="19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I49" s="11">
         <v>0.94910000000000005</v>
@@ -5417,16 +5414,16 @@
     </row>
     <row r="50" spans="2:9" ht="13.15">
       <c r="B50" s="19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I50" s="11">
         <v>0.92969999999999997</v>
@@ -5434,7 +5431,7 @@
     </row>
     <row r="51" spans="2:9" ht="13.15">
       <c r="B51" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F51" s="11" t="str">
         <f>F46</f>
@@ -5445,7 +5442,7 @@
         <v>USD20</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I51" s="11">
         <f t="shared" si="0"/>
@@ -5454,13 +5451,13 @@
     </row>
     <row r="52" spans="2:9" ht="13.15">
       <c r="B52" s="19" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I52" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5468,13 +5465,13 @@
     </row>
     <row r="53" spans="2:9" ht="13.15">
       <c r="B53" s="19" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I53" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5482,13 +5479,13 @@
     </row>
     <row r="54" spans="2:9" ht="13.15">
       <c r="B54" s="19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I54" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5496,10 +5493,10 @@
     </row>
     <row r="55" spans="2:9">
       <c r="F55" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I55" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5507,10 +5504,10 @@
     </row>
     <row r="56" spans="2:9">
       <c r="F56" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I56" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5518,10 +5515,10 @@
     </row>
     <row r="57" spans="2:9">
       <c r="F57" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I57" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5529,10 +5526,10 @@
     </row>
     <row r="58" spans="2:9">
       <c r="F58" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I58" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5540,10 +5537,10 @@
     </row>
     <row r="59" spans="2:9">
       <c r="F59" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I59" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5551,10 +5548,10 @@
     </row>
     <row r="60" spans="2:9">
       <c r="F60" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I60" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5562,10 +5559,10 @@
     </row>
     <row r="61" spans="2:9">
       <c r="F61" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I61" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5573,10 +5570,10 @@
     </row>
     <row r="62" spans="2:9">
       <c r="F62" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I62" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5584,10 +5581,10 @@
     </row>
     <row r="63" spans="2:9">
       <c r="F63" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I63" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5595,10 +5592,10 @@
     </row>
     <row r="64" spans="2:9">
       <c r="F64" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I64" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5606,10 +5603,10 @@
     </row>
     <row r="65" spans="6:9">
       <c r="F65" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I65" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5617,10 +5614,10 @@
     </row>
     <row r="66" spans="6:9">
       <c r="F66" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I66" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5628,10 +5625,10 @@
     </row>
     <row r="67" spans="6:9">
       <c r="F67" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I67" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5639,10 +5636,10 @@
     </row>
     <row r="68" spans="6:9">
       <c r="F68" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I68" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5650,10 +5647,10 @@
     </row>
     <row r="69" spans="6:9">
       <c r="F69" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I69" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5661,10 +5658,10 @@
     </row>
     <row r="70" spans="6:9">
       <c r="F70" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I70" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5672,10 +5669,10 @@
     </row>
     <row r="71" spans="6:9">
       <c r="F71" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I71" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5683,10 +5680,10 @@
     </row>
     <row r="72" spans="6:9">
       <c r="F72" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I72" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5694,10 +5691,10 @@
     </row>
     <row r="73" spans="6:9">
       <c r="F73" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I73" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5705,10 +5702,10 @@
     </row>
     <row r="74" spans="6:9">
       <c r="F74" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I74" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5716,10 +5713,10 @@
     </row>
     <row r="75" spans="6:9">
       <c r="F75" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I75" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5727,10 +5724,10 @@
     </row>
     <row r="76" spans="6:9">
       <c r="F76" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I76" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5738,10 +5735,10 @@
     </row>
     <row r="77" spans="6:9">
       <c r="F77" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I77" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5749,10 +5746,10 @@
     </row>
     <row r="78" spans="6:9">
       <c r="F78" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I78" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5760,10 +5757,10 @@
     </row>
     <row r="79" spans="6:9">
       <c r="F79" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I79" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5771,10 +5768,10 @@
     </row>
     <row r="80" spans="6:9">
       <c r="F80" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I80" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5782,10 +5779,10 @@
     </row>
     <row r="81" spans="6:9">
       <c r="F81" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I81" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5793,10 +5790,10 @@
     </row>
     <row r="82" spans="6:9">
       <c r="F82" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I82" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5804,10 +5801,10 @@
     </row>
     <row r="83" spans="6:9">
       <c r="F83" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I83" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5815,10 +5812,10 @@
     </row>
     <row r="84" spans="6:9">
       <c r="F84" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I84" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5826,10 +5823,10 @@
     </row>
     <row r="85" spans="6:9">
       <c r="F85" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I85" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5837,10 +5834,10 @@
     </row>
     <row r="86" spans="6:9">
       <c r="F86" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I86" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5848,10 +5845,10 @@
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I87" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5859,10 +5856,10 @@
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I88" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5870,10 +5867,10 @@
     </row>
     <row r="89" spans="6:9">
       <c r="F89" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I89" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5881,10 +5878,10 @@
     </row>
     <row r="90" spans="6:9">
       <c r="F90" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I90" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5892,10 +5889,10 @@
     </row>
     <row r="91" spans="6:9">
       <c r="F91" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I91" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5903,10 +5900,10 @@
     </row>
     <row r="92" spans="6:9">
       <c r="F92" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I92" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5914,10 +5911,10 @@
     </row>
     <row r="93" spans="6:9">
       <c r="F93" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I93" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5925,10 +5922,10 @@
     </row>
     <row r="94" spans="6:9">
       <c r="F94" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I94" s="11">
         <v>7.0000000000000007E-2</v>
@@ -5936,7 +5933,7 @@
     </row>
     <row r="95" spans="6:9">
       <c r="F95" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H95" s="11" t="str">
         <f>H51</f>
@@ -5948,39 +5945,39 @@
     </row>
     <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
       <c r="E99" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
       <c r="E100" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I100" s="4">
         <v>2022</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="5:10" ht="14.25">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H101" s="21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I101" s="22">
         <f>1.10926234054354*I40</f>
@@ -5990,11 +5987,11 @@
     <row r="102" spans="5:10" ht="14.25">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G102"/>
       <c r="H102" s="21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I102" s="22">
         <f>I84</f>
@@ -6019,26 +6016,26 @@
   <sheetData>
     <row r="3" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B3" s="20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D5" s="6">
         <v>-1</v>
@@ -6046,10 +6043,10 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -6057,10 +6054,10 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -6068,10 +6065,10 @@
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -6079,10 +6076,10 @@
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -6090,10 +6087,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -6101,10 +6098,10 @@
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -6112,10 +6109,10 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -6123,10 +6120,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -6134,10 +6131,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -6145,10 +6142,10 @@
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -6156,10 +6153,10 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D16" s="16">
         <v>1.0000000000000001E-5</v>
@@ -6167,10 +6164,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D17" s="16">
         <v>1.0000000000000001E-5</v>
@@ -6178,10 +6175,10 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D18" s="16">
         <v>1.0000000000000001E-5</v>
@@ -6189,10 +6186,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D19" s="16">
         <v>1.0000000000000001E-5</v>
@@ -6200,10 +6197,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D20" s="17">
         <v>1</v>
@@ -6211,73 +6208,73 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B25" s="20" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6975D90-B59D-4D67-9B99-3DA9DE80D7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F2B3E0-AD7E-424E-9A6C-E11DFF3E40DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F2B3E0-AD7E-424E-9A6C-E11DFF3E40DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2893128C-C884-4BBE-B99B-3878E716C511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2893128C-C884-4BBE-B99B-3878E716C511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D295AAC4-D5F2-46FB-BF06-BCE4FCEC552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D295AAC4-D5F2-46FB-BF06-BCE4FCEC552F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDD4D0-A8AF-4FE9-B6EE-01F0A3047B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDD4D0-A8AF-4FE9-B6EE-01F0A3047B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E57135A-AE8F-42F9-8DC4-D9D82239D9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E57135A-AE8F-42F9-8DC4-D9D82239D9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A01A480-8F64-443C-99A0-03FE6601D3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A01A480-8F64-443C-99A0-03FE6601D3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3E4766-06E1-4AFA-A77F-D25F46E74A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND/SysSettings.xlsx
+++ b/VerveStacks_IND/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3E4766-06E1-4AFA-A77F-D25F46E74A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2BBFCA-33F3-404A-904A-E6E49534B9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="554">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -676,31 +676,1030 @@
     <t>OIL</t>
   </si>
   <si>
+    <t>cap_bnd</t>
+  </si>
+  <si>
     <t>IND</t>
   </si>
   <si>
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv-IND</t>
-  </si>
-  <si>
-    <t>solar electricity generation</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_wof-IND</t>
-  </si>
-  <si>
-    <t>offshore wind electricity generation</t>
-  </si>
-  <si>
-    <t>elc_won-IND</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation</t>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_spv_032</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_spv_033</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_spv_034</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_spv_035</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_spv_036</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_spv_037</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_spv_038</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_spv_039</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_spv_040</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_spv_041</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_spv_042</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_spv_043</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_spv_044</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_spv_045</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_spv_046</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_spv_047</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_spv_048</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_spv_049</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_spv_050</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_spv_051</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_spv_052</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 52</t>
+  </si>
+  <si>
+    <t>elc_spv_053</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 53</t>
+  </si>
+  <si>
+    <t>elc_spv_054</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 54</t>
+  </si>
+  <si>
+    <t>elc_spv_055</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 55</t>
+  </si>
+  <si>
+    <t>elc_spv_056</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 56</t>
+  </si>
+  <si>
+    <t>elc_spv_057</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 57</t>
+  </si>
+  <si>
+    <t>elc_spv_058</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 58</t>
+  </si>
+  <si>
+    <t>elc_spv_059</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 59</t>
+  </si>
+  <si>
+    <t>elc_spv_060</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 60</t>
+  </si>
+  <si>
+    <t>elc_spv_061</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 61</t>
+  </si>
+  <si>
+    <t>elc_spv_062</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 62</t>
+  </si>
+  <si>
+    <t>elc_spv_063</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 63</t>
+  </si>
+  <si>
+    <t>elc_spv_064</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 64</t>
+  </si>
+  <si>
+    <t>elc_spv_065</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 65</t>
+  </si>
+  <si>
+    <t>elc_spv_066</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 66</t>
+  </si>
+  <si>
+    <t>elc_spv_067</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 67</t>
+  </si>
+  <si>
+    <t>elc_spv_068</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 68</t>
+  </si>
+  <si>
+    <t>elc_spv_069</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 69</t>
+  </si>
+  <si>
+    <t>elc_spv_070</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 70</t>
+  </si>
+  <si>
+    <t>elc_spv_071</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 71</t>
+  </si>
+  <si>
+    <t>elc_spv_072</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 72</t>
+  </si>
+  <si>
+    <t>elc_spv_073</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 73</t>
+  </si>
+  <si>
+    <t>elc_spv_074</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 74</t>
+  </si>
+  <si>
+    <t>elc_spv_075</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 75</t>
+  </si>
+  <si>
+    <t>elc_spv_076</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 76</t>
+  </si>
+  <si>
+    <t>elc_spv_077</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 77</t>
+  </si>
+  <si>
+    <t>elc_spv_078</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 78</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 52</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 53</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 54</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 55</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 56</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 57</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 58</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 59</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 60</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 61</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 62</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 63</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 64</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 65</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 66</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 67</t>
   </si>
 </sst>
 </file>
@@ -3091,7 +4090,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3116,7 +4115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R24"/>
+  <dimension ref="B3:R173"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -3174,7 +4173,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3206,10 +4205,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3218,7 +4217,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3235,10 +4234,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3247,7 +4246,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3264,10 +4263,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3276,7 +4275,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3289,6 +4288,24 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>222</v>
+      </c>
+      <c r="O8" t="s">
+        <v>223</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="s">
@@ -3300,6 +4317,24 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>224</v>
+      </c>
+      <c r="O9" t="s">
+        <v>225</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" t="s">
@@ -3311,6 +4346,24 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>226</v>
+      </c>
+      <c r="O10" t="s">
+        <v>227</v>
+      </c>
+      <c r="P10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" t="s">
@@ -3322,6 +4375,24 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>228</v>
+      </c>
+      <c r="O11" t="s">
+        <v>229</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" t="s">
@@ -3333,6 +4404,24 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>230</v>
+      </c>
+      <c r="O12" t="s">
+        <v>231</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" t="s">
@@ -3344,6 +4433,24 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>232</v>
+      </c>
+      <c r="O13" t="s">
+        <v>233</v>
+      </c>
+      <c r="P13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -3358,6 +4465,24 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>234</v>
+      </c>
+      <c r="O14" t="s">
+        <v>235</v>
+      </c>
+      <c r="P14" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" t="s">
@@ -3372,6 +4497,24 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>236</v>
+      </c>
+      <c r="O15" t="s">
+        <v>237</v>
+      </c>
+      <c r="P15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="16" spans="2:18">
       <c r="B16" t="s">
@@ -3395,8 +4538,26 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>238</v>
+      </c>
+      <c r="O16" t="s">
+        <v>239</v>
+      </c>
+      <c r="P16" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3409,8 +4570,26 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>240</v>
+      </c>
+      <c r="O17" t="s">
+        <v>241</v>
+      </c>
+      <c r="P17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3423,8 +4602,26 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>242</v>
+      </c>
+      <c r="O18" t="s">
+        <v>243</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3437,8 +4634,26 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>244</v>
+      </c>
+      <c r="O19" t="s">
+        <v>245</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3451,8 +4666,26 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>246</v>
+      </c>
+      <c r="O20" t="s">
+        <v>247</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -3471,8 +4704,26 @@
       <c r="G21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="M21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>248</v>
+      </c>
+      <c r="O21" t="s">
+        <v>249</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>193</v>
       </c>
@@ -3485,8 +4736,26 @@
       <c r="E22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>250</v>
+      </c>
+      <c r="O22" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -3496,8 +4765,26 @@
       <c r="E23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>252</v>
+      </c>
+      <c r="O23" t="s">
+        <v>253</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>193</v>
       </c>
@@ -3506,6 +4793,3004 @@
       </c>
       <c r="E24" t="s">
         <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>254</v>
+      </c>
+      <c r="O24" t="s">
+        <v>255</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>256</v>
+      </c>
+      <c r="O25" t="s">
+        <v>257</v>
+      </c>
+      <c r="P25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>258</v>
+      </c>
+      <c r="O26" t="s">
+        <v>259</v>
+      </c>
+      <c r="P26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>260</v>
+      </c>
+      <c r="O27" t="s">
+        <v>261</v>
+      </c>
+      <c r="P27" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>262</v>
+      </c>
+      <c r="O28" t="s">
+        <v>263</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>264</v>
+      </c>
+      <c r="O29" t="s">
+        <v>265</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>266</v>
+      </c>
+      <c r="O30" t="s">
+        <v>267</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>268</v>
+      </c>
+      <c r="O31" t="s">
+        <v>269</v>
+      </c>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>270</v>
+      </c>
+      <c r="O32" t="s">
+        <v>271</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>272</v>
+      </c>
+      <c r="O33" t="s">
+        <v>273</v>
+      </c>
+      <c r="P33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>274</v>
+      </c>
+      <c r="O34" t="s">
+        <v>275</v>
+      </c>
+      <c r="P34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="13:18">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>276</v>
+      </c>
+      <c r="O35" t="s">
+        <v>277</v>
+      </c>
+      <c r="P35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="13:18">
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>278</v>
+      </c>
+      <c r="O36" t="s">
+        <v>279</v>
+      </c>
+      <c r="P36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="13:18">
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>280</v>
+      </c>
+      <c r="O37" t="s">
+        <v>281</v>
+      </c>
+      <c r="P37" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="13:18">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>282</v>
+      </c>
+      <c r="O38" t="s">
+        <v>283</v>
+      </c>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="13:18">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>284</v>
+      </c>
+      <c r="O39" t="s">
+        <v>285</v>
+      </c>
+      <c r="P39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="13:18">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>286</v>
+      </c>
+      <c r="O40" t="s">
+        <v>287</v>
+      </c>
+      <c r="P40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="13:18">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>288</v>
+      </c>
+      <c r="O41" t="s">
+        <v>289</v>
+      </c>
+      <c r="P41" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="13:18">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>290</v>
+      </c>
+      <c r="O42" t="s">
+        <v>291</v>
+      </c>
+      <c r="P42" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="13:18">
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>292</v>
+      </c>
+      <c r="O43" t="s">
+        <v>293</v>
+      </c>
+      <c r="P43" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>35</v>
+      </c>
+      <c r="R43" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="13:18">
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>294</v>
+      </c>
+      <c r="O44" t="s">
+        <v>295</v>
+      </c>
+      <c r="P44" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>35</v>
+      </c>
+      <c r="R44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="13:18">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>296</v>
+      </c>
+      <c r="O45" t="s">
+        <v>297</v>
+      </c>
+      <c r="P45" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="13:18">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>298</v>
+      </c>
+      <c r="O46" t="s">
+        <v>299</v>
+      </c>
+      <c r="P46" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="13:18">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>300</v>
+      </c>
+      <c r="O47" t="s">
+        <v>301</v>
+      </c>
+      <c r="P47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="13:18">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>302</v>
+      </c>
+      <c r="O48" t="s">
+        <v>303</v>
+      </c>
+      <c r="P48" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="13:18">
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>304</v>
+      </c>
+      <c r="O49" t="s">
+        <v>305</v>
+      </c>
+      <c r="P49" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="13:18">
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>306</v>
+      </c>
+      <c r="O50" t="s">
+        <v>307</v>
+      </c>
+      <c r="P50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="13:18">
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>308</v>
+      </c>
+      <c r="O51" t="s">
+        <v>309</v>
+      </c>
+      <c r="P51" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="13:18">
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>310</v>
+      </c>
+      <c r="O52" t="s">
+        <v>311</v>
+      </c>
+      <c r="P52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>35</v>
+      </c>
+      <c r="R52" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>312</v>
+      </c>
+      <c r="O53" t="s">
+        <v>313</v>
+      </c>
+      <c r="P53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="13:18">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>314</v>
+      </c>
+      <c r="O54" t="s">
+        <v>315</v>
+      </c>
+      <c r="P54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>35</v>
+      </c>
+      <c r="R54" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="13:18">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>316</v>
+      </c>
+      <c r="O55" t="s">
+        <v>317</v>
+      </c>
+      <c r="P55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="13:18">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>318</v>
+      </c>
+      <c r="O56" t="s">
+        <v>319</v>
+      </c>
+      <c r="P56" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R56" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="13:18">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>320</v>
+      </c>
+      <c r="O57" t="s">
+        <v>321</v>
+      </c>
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="13:18">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>322</v>
+      </c>
+      <c r="O58" t="s">
+        <v>323</v>
+      </c>
+      <c r="P58" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="59" spans="13:18">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>324</v>
+      </c>
+      <c r="O59" t="s">
+        <v>325</v>
+      </c>
+      <c r="P59" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="13:18">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>326</v>
+      </c>
+      <c r="O60" t="s">
+        <v>327</v>
+      </c>
+      <c r="P60" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>328</v>
+      </c>
+      <c r="O61" t="s">
+        <v>329</v>
+      </c>
+      <c r="P61" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>330</v>
+      </c>
+      <c r="O62" t="s">
+        <v>331</v>
+      </c>
+      <c r="P62" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="13:18">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>332</v>
+      </c>
+      <c r="O63" t="s">
+        <v>333</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="13:18">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>334</v>
+      </c>
+      <c r="O64" t="s">
+        <v>335</v>
+      </c>
+      <c r="P64" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" spans="13:18">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>336</v>
+      </c>
+      <c r="O65" t="s">
+        <v>337</v>
+      </c>
+      <c r="P65" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="13:18">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>338</v>
+      </c>
+      <c r="O66" t="s">
+        <v>339</v>
+      </c>
+      <c r="P66" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="13:18">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>340</v>
+      </c>
+      <c r="O67" t="s">
+        <v>341</v>
+      </c>
+      <c r="P67" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>35</v>
+      </c>
+      <c r="R67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="13:18">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>342</v>
+      </c>
+      <c r="O68" t="s">
+        <v>343</v>
+      </c>
+      <c r="P68" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="13:18">
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>344</v>
+      </c>
+      <c r="O69" t="s">
+        <v>345</v>
+      </c>
+      <c r="P69" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>35</v>
+      </c>
+      <c r="R69" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="13:18">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>346</v>
+      </c>
+      <c r="O70" t="s">
+        <v>347</v>
+      </c>
+      <c r="P70" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>35</v>
+      </c>
+      <c r="R70" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="13:18">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>348</v>
+      </c>
+      <c r="O71" t="s">
+        <v>349</v>
+      </c>
+      <c r="P71" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>35</v>
+      </c>
+      <c r="R71" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="13:18">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>350</v>
+      </c>
+      <c r="O72" t="s">
+        <v>351</v>
+      </c>
+      <c r="P72" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>35</v>
+      </c>
+      <c r="R72" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="13:18">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>352</v>
+      </c>
+      <c r="O73" t="s">
+        <v>353</v>
+      </c>
+      <c r="P73" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>35</v>
+      </c>
+      <c r="R73" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="13:18">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>354</v>
+      </c>
+      <c r="O74" t="s">
+        <v>355</v>
+      </c>
+      <c r="P74" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>35</v>
+      </c>
+      <c r="R74" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="75" spans="13:18">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>356</v>
+      </c>
+      <c r="O75" t="s">
+        <v>357</v>
+      </c>
+      <c r="P75" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>35</v>
+      </c>
+      <c r="R75" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="76" spans="13:18">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>358</v>
+      </c>
+      <c r="O76" t="s">
+        <v>359</v>
+      </c>
+      <c r="P76" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>35</v>
+      </c>
+      <c r="R76" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="77" spans="13:18">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>360</v>
+      </c>
+      <c r="O77" t="s">
+        <v>361</v>
+      </c>
+      <c r="P77" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>35</v>
+      </c>
+      <c r="R77" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="13:18">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>362</v>
+      </c>
+      <c r="O78" t="s">
+        <v>363</v>
+      </c>
+      <c r="P78" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>35</v>
+      </c>
+      <c r="R78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="13:18">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>364</v>
+      </c>
+      <c r="O79" t="s">
+        <v>365</v>
+      </c>
+      <c r="P79" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>35</v>
+      </c>
+      <c r="R79" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="13:18">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>366</v>
+      </c>
+      <c r="O80" t="s">
+        <v>367</v>
+      </c>
+      <c r="P80" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>35</v>
+      </c>
+      <c r="R80" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="13:18">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>368</v>
+      </c>
+      <c r="O81" t="s">
+        <v>369</v>
+      </c>
+      <c r="P81" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="13:18">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>370</v>
+      </c>
+      <c r="O82" t="s">
+        <v>371</v>
+      </c>
+      <c r="P82" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>35</v>
+      </c>
+      <c r="R82" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="83" spans="13:18">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>372</v>
+      </c>
+      <c r="O83" t="s">
+        <v>373</v>
+      </c>
+      <c r="P83" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>35</v>
+      </c>
+      <c r="R83" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="84" spans="13:18">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>374</v>
+      </c>
+      <c r="O84" t="s">
+        <v>375</v>
+      </c>
+      <c r="P84" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>35</v>
+      </c>
+      <c r="R84" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="13:18">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>376</v>
+      </c>
+      <c r="O85" t="s">
+        <v>377</v>
+      </c>
+      <c r="P85" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="13:18">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>378</v>
+      </c>
+      <c r="O86" t="s">
+        <v>379</v>
+      </c>
+      <c r="P86" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>35</v>
+      </c>
+      <c r="R86" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="13:18">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>380</v>
+      </c>
+      <c r="O87" t="s">
+        <v>381</v>
+      </c>
+      <c r="P87" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="88" spans="13:18">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>382</v>
+      </c>
+      <c r="O88" t="s">
+        <v>383</v>
+      </c>
+      <c r="P88" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>35</v>
+      </c>
+      <c r="R88" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" spans="13:18">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>384</v>
+      </c>
+      <c r="O89" t="s">
+        <v>385</v>
+      </c>
+      <c r="P89" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="13:18">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>386</v>
+      </c>
+      <c r="O90" t="s">
+        <v>387</v>
+      </c>
+      <c r="P90" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>35</v>
+      </c>
+      <c r="R90" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="13:18">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>388</v>
+      </c>
+      <c r="O91" t="s">
+        <v>389</v>
+      </c>
+      <c r="P91" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>35</v>
+      </c>
+      <c r="R91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="13:18">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>390</v>
+      </c>
+      <c r="O92" t="s">
+        <v>391</v>
+      </c>
+      <c r="P92" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>35</v>
+      </c>
+      <c r="R92" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="13:18">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>392</v>
+      </c>
+      <c r="O93" t="s">
+        <v>393</v>
+      </c>
+      <c r="P93" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>35</v>
+      </c>
+      <c r="R93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="13:18">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>394</v>
+      </c>
+      <c r="O94" t="s">
+        <v>395</v>
+      </c>
+      <c r="P94" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="13:18">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>396</v>
+      </c>
+      <c r="O95" t="s">
+        <v>397</v>
+      </c>
+      <c r="P95" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>35</v>
+      </c>
+      <c r="R95" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="96" spans="13:18">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>398</v>
+      </c>
+      <c r="O96" t="s">
+        <v>399</v>
+      </c>
+      <c r="P96" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>35</v>
+      </c>
+      <c r="R96" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="13:18">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>400</v>
+      </c>
+      <c r="O97" t="s">
+        <v>401</v>
+      </c>
+      <c r="P97" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>35</v>
+      </c>
+      <c r="R97" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="13:18">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>402</v>
+      </c>
+      <c r="O98" t="s">
+        <v>403</v>
+      </c>
+      <c r="P98" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>35</v>
+      </c>
+      <c r="R98" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="13:18">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>404</v>
+      </c>
+      <c r="O99" t="s">
+        <v>405</v>
+      </c>
+      <c r="P99" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>35</v>
+      </c>
+      <c r="R99" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="13:18">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>406</v>
+      </c>
+      <c r="O100" t="s">
+        <v>407</v>
+      </c>
+      <c r="P100" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>35</v>
+      </c>
+      <c r="R100" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="13:18">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>408</v>
+      </c>
+      <c r="O101" t="s">
+        <v>409</v>
+      </c>
+      <c r="P101" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="13:18">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>410</v>
+      </c>
+      <c r="O102" t="s">
+        <v>411</v>
+      </c>
+      <c r="P102" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="13:18">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>412</v>
+      </c>
+      <c r="O103" t="s">
+        <v>413</v>
+      </c>
+      <c r="P103" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>35</v>
+      </c>
+      <c r="R103" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="13:18">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>414</v>
+      </c>
+      <c r="O104" t="s">
+        <v>415</v>
+      </c>
+      <c r="P104" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="105" spans="13:18">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>416</v>
+      </c>
+      <c r="O105" t="s">
+        <v>417</v>
+      </c>
+      <c r="P105" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>35</v>
+      </c>
+      <c r="R105" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="13:18">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>418</v>
+      </c>
+      <c r="O106" t="s">
+        <v>419</v>
+      </c>
+      <c r="P106" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>35</v>
+      </c>
+      <c r="R106" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="107" spans="13:18">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>420</v>
+      </c>
+      <c r="O107" t="s">
+        <v>421</v>
+      </c>
+      <c r="P107" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>35</v>
+      </c>
+      <c r="R107" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="108" spans="13:18">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>422</v>
+      </c>
+      <c r="O108" t="s">
+        <v>423</v>
+      </c>
+      <c r="P108" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>35</v>
+      </c>
+      <c r="R108" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" spans="13:18">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>424</v>
+      </c>
+      <c r="O109" t="s">
+        <v>425</v>
+      </c>
+      <c r="P109" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>35</v>
+      </c>
+      <c r="R109" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="13:18">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>426</v>
+      </c>
+      <c r="O110" t="s">
+        <v>427</v>
+      </c>
+      <c r="P110" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>35</v>
+      </c>
+      <c r="R110" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="111" spans="13:18">
+      <c r="M111" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>428</v>
+      </c>
+      <c r="O111" t="s">
+        <v>429</v>
+      </c>
+      <c r="P111" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>35</v>
+      </c>
+      <c r="R111" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="13:18">
+      <c r="M112" t="s">
+        <v>17</v>
+      </c>
+      <c r="N112" t="s">
+        <v>430</v>
+      </c>
+      <c r="O112" t="s">
+        <v>431</v>
+      </c>
+      <c r="P112" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>35</v>
+      </c>
+      <c r="R112" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="113" spans="13:18">
+      <c r="M113" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" t="s">
+        <v>432</v>
+      </c>
+      <c r="O113" t="s">
+        <v>433</v>
+      </c>
+      <c r="P113" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>35</v>
+      </c>
+      <c r="R113" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="114" spans="13:18">
+      <c r="M114" t="s">
+        <v>17</v>
+      </c>
+      <c r="N114" t="s">
+        <v>434</v>
+      </c>
+      <c r="O114" t="s">
+        <v>435</v>
+      </c>
+      <c r="P114" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>35</v>
+      </c>
+      <c r="R114" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="115" spans="13:18">
+      <c r="M115" t="s">
+        <v>17</v>
+      </c>
+      <c r="N115" t="s">
+        <v>436</v>
+      </c>
+      <c r="O115" t="s">
+        <v>437</v>
+      </c>
+      <c r="P115" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>35</v>
+      </c>
+      <c r="R115" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="116" spans="13:18">
+      <c r="M116" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" t="s">
+        <v>438</v>
+      </c>
+      <c r="O116" t="s">
+        <v>439</v>
+      </c>
+      <c r="P116" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>35</v>
+      </c>
+      <c r="R116" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="117" spans="13:18">
+      <c r="M117" t="s">
+        <v>17</v>
+      </c>
+      <c r="N117" t="s">
+        <v>440</v>
+      </c>
+      <c r="O117" t="s">
+        <v>441</v>
+      </c>
+      <c r="P117" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>35</v>
+      </c>
+      <c r="R117" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="118" spans="13:18">
+      <c r="M118" t="s">
+        <v>17</v>
+      </c>
+      <c r="N118" t="s">
+        <v>442</v>
+      </c>
+      <c r="O118" t="s">
+        <v>443</v>
+      </c>
+      <c r="P118" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>35</v>
+      </c>
+      <c r="R118" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="119" spans="13:18">
+      <c r="M119" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119" t="s">
+        <v>444</v>
+      </c>
+      <c r="O119" t="s">
+        <v>445</v>
+      </c>
+      <c r="P119" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>35</v>
+      </c>
+      <c r="R119" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="120" spans="13:18">
+      <c r="M120" t="s">
+        <v>17</v>
+      </c>
+      <c r="N120" t="s">
+        <v>446</v>
+      </c>
+      <c r="O120" t="s">
+        <v>447</v>
+      </c>
+      <c r="P120" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>35</v>
+      </c>
+      <c r="R120" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="121" spans="13:18">
+      <c r="M121" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" t="s">
+        <v>448</v>
+      </c>
+      <c r="O121" t="s">
+        <v>449</v>
+      </c>
+      <c r="P121" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>35</v>
+      </c>
+      <c r="R121" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="13:18">
+      <c r="M122" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" t="s">
+        <v>450</v>
+      </c>
+      <c r="O122" t="s">
+        <v>451</v>
+      </c>
+      <c r="P122" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>35</v>
+      </c>
+      <c r="R122" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="123" spans="13:18">
+      <c r="M123" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123" t="s">
+        <v>452</v>
+      </c>
+      <c r="O123" t="s">
+        <v>453</v>
+      </c>
+      <c r="P123" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>35</v>
+      </c>
+      <c r="R123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="13:18">
+      <c r="M124" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" t="s">
+        <v>454</v>
+      </c>
+      <c r="O124" t="s">
+        <v>455</v>
+      </c>
+      <c r="P124" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>35</v>
+      </c>
+      <c r="R124" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="125" spans="13:18">
+      <c r="M125" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" t="s">
+        <v>456</v>
+      </c>
+      <c r="O125" t="s">
+        <v>457</v>
+      </c>
+      <c r="P125" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>35</v>
+      </c>
+      <c r="R125" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="126" spans="13:18">
+      <c r="M126" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" t="s">
+        <v>458</v>
+      </c>
+      <c r="O126" t="s">
+        <v>459</v>
+      </c>
+      <c r="P126" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>35</v>
+      </c>
+      <c r="R126" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="127" spans="13:18">
+      <c r="M127" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" t="s">
+        <v>460</v>
+      </c>
+      <c r="O127" t="s">
+        <v>461</v>
+      </c>
+      <c r="P127" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>35</v>
+      </c>
+      <c r="R127" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="128" spans="13:18">
+      <c r="M128" t="s">
+        <v>17</v>
+      </c>
+      <c r="N128" t="s">
+        <v>462</v>
+      </c>
+      <c r="O128" t="s">
+        <v>463</v>
+      </c>
+      <c r="P128" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>35</v>
+      </c>
+      <c r="R128" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="129" spans="13:18">
+      <c r="M129" t="s">
+        <v>17</v>
+      </c>
+      <c r="N129" t="s">
+        <v>464</v>
+      </c>
+      <c r="O129" t="s">
+        <v>465</v>
+      </c>
+      <c r="P129" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>35</v>
+      </c>
+      <c r="R129" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" spans="13:18">
+      <c r="M130" t="s">
+        <v>17</v>
+      </c>
+      <c r="N130" t="s">
+        <v>466</v>
+      </c>
+      <c r="O130" t="s">
+        <v>467</v>
+      </c>
+      <c r="P130" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>35</v>
+      </c>
+      <c r="R130" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="131" spans="13:18">
+      <c r="M131" t="s">
+        <v>17</v>
+      </c>
+      <c r="N131" t="s">
+        <v>468</v>
+      </c>
+      <c r="O131" t="s">
+        <v>469</v>
+      </c>
+      <c r="P131" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>35</v>
+      </c>
+      <c r="R131" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="13:18">
+      <c r="M132" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132" t="s">
+        <v>470</v>
+      </c>
+      <c r="O132" t="s">
+        <v>471</v>
+      </c>
+      <c r="P132" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>35</v>
+      </c>
+      <c r="R132" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="133" spans="13:18">
+      <c r="M133" t="s">
+        <v>17</v>
+      </c>
+      <c r="N133" t="s">
+        <v>472</v>
+      </c>
+      <c r="O133" t="s">
+        <v>473</v>
+      </c>
+      <c r="P133" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>35</v>
+      </c>
+      <c r="R133" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="134" spans="13:18">
+      <c r="M134" t="s">
+        <v>17</v>
+      </c>
+      <c r="N134" t="s">
+        <v>474</v>
+      </c>
+      <c r="O134" t="s">
+        <v>475</v>
+      </c>
+      <c r="P134" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>35</v>
+      </c>
+      <c r="R134" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="135" spans="13:18">
+      <c r="M135" t="s">
+        <v>17</v>
+      </c>
+      <c r="N135" t="s">
+        <v>476</v>
+      </c>
+      <c r="O135" t="s">
+        <v>477</v>
+      </c>
+      <c r="P135" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>35</v>
+      </c>
+      <c r="R135" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="136" spans="13:18">
+      <c r="M136" t="s">
+        <v>17</v>
+      </c>
+      <c r="N136" t="s">
+        <v>478</v>
+      </c>
+      <c r="O136" t="s">
+        <v>479</v>
+      </c>
+      <c r="P136" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>35</v>
+      </c>
+      <c r="R136" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="137" spans="13:18">
+      <c r="M137" t="s">
+        <v>17</v>
+      </c>
+      <c r="N137" t="s">
+        <v>480</v>
+      </c>
+      <c r="O137" t="s">
+        <v>481</v>
+      </c>
+      <c r="P137" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>35</v>
+      </c>
+      <c r="R137" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="138" spans="13:18">
+      <c r="M138" t="s">
+        <v>17</v>
+      </c>
+      <c r="N138" t="s">
+        <v>482</v>
+      </c>
+      <c r="O138" t="s">
+        <v>483</v>
+      </c>
+      <c r="P138" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>35</v>
+      </c>
+      <c r="R138" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="139" spans="13:18">
+      <c r="M139" t="s">
+        <v>17</v>
+      </c>
+      <c r="N139" t="s">
+        <v>484</v>
+      </c>
+      <c r="O139" t="s">
+        <v>485</v>
+      </c>
+      <c r="P139" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>35</v>
+      </c>
+      <c r="R139" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="140" spans="13:18">
+      <c r="M140" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" t="s">
+        <v>486</v>
+      </c>
+      <c r="O140" t="s">
+        <v>487</v>
+      </c>
+      <c r="P140" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>35</v>
+      </c>
+      <c r="R140" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="141" spans="13:18">
+      <c r="M141" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" t="s">
+        <v>488</v>
+      </c>
+      <c r="O141" t="s">
+        <v>489</v>
+      </c>
+      <c r="P141" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>35</v>
+      </c>
+      <c r="R141" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="142" spans="13:18">
+      <c r="M142" t="s">
+        <v>17</v>
+      </c>
+      <c r="N142" t="s">
+        <v>490</v>
+      </c>
+      <c r="O142" t="s">
+        <v>491</v>
+      </c>
+      <c r="P142" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>35</v>
+      </c>
+      <c r="R142" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="143" spans="13:18">
+      <c r="M143" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" t="s">
+        <v>492</v>
+      </c>
+      <c r="O143" t="s">
+        <v>493</v>
+      </c>
+      <c r="P143" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>35</v>
+      </c>
+      <c r="R143" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="144" spans="13:18">
+      <c r="M144" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" t="s">
+        <v>494</v>
+      </c>
+      <c r="O144" t="s">
+        <v>495</v>
+      </c>
+      <c r="P144" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>35</v>
+      </c>
+      <c r="R144" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="13:18">
+      <c r="M145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" t="s">
+        <v>496</v>
+      </c>
+      <c r="O145" t="s">
+        <v>497</v>
+      </c>
+      <c r="P145" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>35</v>
+      </c>
+      <c r="R145" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="146" spans="13:18">
+      <c r="M146" t="s">
+        <v>17</v>
+      </c>
+      <c r="N146" t="s">
+        <v>498</v>
+      </c>
+      <c r="O146" t="s">
+        <v>499</v>
+      </c>
+      <c r="P146" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>35</v>
+      </c>
+      <c r="R146" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="147" spans="13:18">
+      <c r="M147" t="s">
+        <v>17</v>
+      </c>
+      <c r="N147" t="s">
+        <v>500</v>
+      </c>
+      <c r="O147" t="s">
+        <v>501</v>
+      </c>
+      <c r="P147" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>35</v>
+      </c>
+      <c r="R147" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="148" spans="13:18">
+      <c r="M148" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" t="s">
+        <v>502</v>
+      </c>
+      <c r="O148" t="s">
+        <v>503</v>
+      </c>
+      <c r="P148" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>35</v>
+      </c>
+      <c r="R148" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="149" spans="13:18">
+      <c r="M149" t="s">
+        <v>17</v>
+      </c>
+      <c r="N149" t="s">
+        <v>504</v>
+      </c>
+      <c r="O149" t="s">
+        <v>505</v>
+      </c>
+      <c r="P149" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>35</v>
+      </c>
+      <c r="R149" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="150" spans="13:18">
+      <c r="M150" t="s">
+        <v>17</v>
+      </c>
+      <c r="N150" t="s">
+        <v>506</v>
+      </c>
+      <c r="O150" t="s">
+        <v>507</v>
+      </c>
+      <c r="P150" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>35</v>
+      </c>
+      <c r="R150" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="151" spans="13:18">
+      <c r="M151" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" t="s">
+        <v>508</v>
+      </c>
+      <c r="O151" t="s">
+        <v>509</v>
+      </c>
+      <c r="P151" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>35</v>
+      </c>
+      <c r="R151" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="152" spans="13:18">
+      <c r="M152" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" t="s">
+        <v>510</v>
+      </c>
+      <c r="O152" t="s">
+        <v>511</v>
+      </c>
+      <c r="P152" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>35</v>
+      </c>
+      <c r="R152" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="153" spans="13:18">
+      <c r="M153" t="s">
+        <v>17</v>
+      </c>
+      <c r="N153" t="s">
+        <v>512</v>
+      </c>
+      <c r="O153" t="s">
+        <v>513</v>
+      </c>
+      <c r="P153" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>35</v>
+      </c>
+      <c r="R153" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="154" spans="13:18">
+      <c r="M154" t="s">
+        <v>17</v>
+      </c>
+      <c r="N154" t="s">
+        <v>514</v>
+      </c>
+      <c r="O154" t="s">
+        <v>515</v>
+      </c>
+      <c r="P154" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>35</v>
+      </c>
+      <c r="R154" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="155" spans="13:18">
+      <c r="M155" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" t="s">
+        <v>516</v>
+      </c>
+      <c r="O155" t="s">
+        <v>517</v>
+      </c>
+      <c r="P155" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>35</v>
+      </c>
+      <c r="R155" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="156" spans="13:18">
+      <c r="M156" t="s">
+        <v>17</v>
+      </c>
+      <c r="N156" t="s">
+        <v>518</v>
+      </c>
+      <c r="O156" t="s">
+        <v>519</v>
+      </c>
+      <c r="P156" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>35</v>
+      </c>
+      <c r="R156" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="157" spans="13:18">
+      <c r="M157" t="s">
+        <v>17</v>
+      </c>
+      <c r="N157" t="s">
+        <v>520</v>
+      </c>
+      <c r="O157" t="s">
+        <v>521</v>
+      </c>
+      <c r="P157" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>35</v>
+      </c>
+      <c r="R157" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="158" spans="13:18">
+      <c r="M158" t="s">
+        <v>17</v>
+      </c>
+      <c r="N158" t="s">
+        <v>522</v>
+      </c>
+      <c r="O158" t="s">
+        <v>523</v>
+      </c>
+      <c r="P158" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>35</v>
+      </c>
+      <c r="R158" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="159" spans="13:18">
+      <c r="M159" t="s">
+        <v>17</v>
+      </c>
+      <c r="N159" t="s">
+        <v>524</v>
+      </c>
+      <c r="O159" t="s">
+        <v>525</v>
+      </c>
+      <c r="P159" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>35</v>
+      </c>
+      <c r="R159" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="160" spans="13:18">
+      <c r="M160" t="s">
+        <v>17</v>
+      </c>
+      <c r="N160" t="s">
+        <v>526</v>
+      </c>
+      <c r="O160" t="s">
+        <v>527</v>
+      </c>
+      <c r="P160" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>35</v>
+      </c>
+      <c r="R160" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="161" spans="13:18">
+      <c r="M161" t="s">
+        <v>17</v>
+      </c>
+      <c r="N161" t="s">
+        <v>528</v>
+      </c>
+      <c r="O161" t="s">
+        <v>529</v>
+      </c>
+      <c r="P161" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>35</v>
+      </c>
+      <c r="R161" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="162" spans="13:18">
+      <c r="M162" t="s">
+        <v>17</v>
+      </c>
+      <c r="N162" t="s">
+        <v>530</v>
+      </c>
+      <c r="O162" t="s">
+        <v>531</v>
+      </c>
+      <c r="P162" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>35</v>
+      </c>
+      <c r="R162" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="163" spans="13:18">
+      <c r="M163" t="s">
+        <v>17</v>
+      </c>
+      <c r="N163" t="s">
+        <v>532</v>
+      </c>
+      <c r="O163" t="s">
+        <v>533</v>
+      </c>
+      <c r="P163" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>35</v>
+      </c>
+      <c r="R163" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="164" spans="13:18">
+      <c r="M164" t="s">
+        <v>17</v>
+      </c>
+      <c r="N164" t="s">
+        <v>534</v>
+      </c>
+      <c r="O164" t="s">
+        <v>535</v>
+      </c>
+      <c r="P164" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>35</v>
+      </c>
+      <c r="R164" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="165" spans="13:18">
+      <c r="M165" t="s">
+        <v>17</v>
+      </c>
+      <c r="N165" t="s">
+        <v>536</v>
+      </c>
+      <c r="O165" t="s">
+        <v>537</v>
+      </c>
+      <c r="P165" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>35</v>
+      </c>
+      <c r="R165" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="166" spans="13:18">
+      <c r="M166" t="s">
+        <v>17</v>
+      </c>
+      <c r="N166" t="s">
+        <v>538</v>
+      </c>
+      <c r="O166" t="s">
+        <v>539</v>
+      </c>
+      <c r="P166" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>35</v>
+      </c>
+      <c r="R166" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="167" spans="13:18">
+      <c r="M167" t="s">
+        <v>17</v>
+      </c>
+      <c r="N167" t="s">
+        <v>540</v>
+      </c>
+      <c r="O167" t="s">
+        <v>541</v>
+      </c>
+      <c r="P167" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>35</v>
+      </c>
+      <c r="R167" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="168" spans="13:18">
+      <c r="M168" t="s">
+        <v>17</v>
+      </c>
+      <c r="N168" t="s">
+        <v>542</v>
+      </c>
+      <c r="O168" t="s">
+        <v>543</v>
+      </c>
+      <c r="P168" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>35</v>
+      </c>
+      <c r="R168" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="169" spans="13:18">
+      <c r="M169" t="s">
+        <v>17</v>
+      </c>
+      <c r="N169" t="s">
+        <v>544</v>
+      </c>
+      <c r="O169" t="s">
+        <v>545</v>
+      </c>
+      <c r="P169" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>35</v>
+      </c>
+      <c r="R169" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="170" spans="13:18">
+      <c r="M170" t="s">
+        <v>17</v>
+      </c>
+      <c r="N170" t="s">
+        <v>546</v>
+      </c>
+      <c r="O170" t="s">
+        <v>547</v>
+      </c>
+      <c r="P170" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>35</v>
+      </c>
+      <c r="R170" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="171" spans="13:18">
+      <c r="M171" t="s">
+        <v>17</v>
+      </c>
+      <c r="N171" t="s">
+        <v>548</v>
+      </c>
+      <c r="O171" t="s">
+        <v>549</v>
+      </c>
+      <c r="P171" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>35</v>
+      </c>
+      <c r="R171" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="172" spans="13:18">
+      <c r="M172" t="s">
+        <v>17</v>
+      </c>
+      <c r="N172" t="s">
+        <v>550</v>
+      </c>
+      <c r="O172" t="s">
+        <v>551</v>
+      </c>
+      <c r="P172" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>35</v>
+      </c>
+      <c r="R172" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="173" spans="13:18">
+      <c r="M173" t="s">
+        <v>17</v>
+      </c>
+      <c r="N173" t="s">
+        <v>552</v>
+      </c>
+      <c r="O173" t="s">
+        <v>553</v>
+      </c>
+      <c r="P173" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>35</v>
+      </c>
+      <c r="R173" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3796,7 +8081,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -3938,49 +8223,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="14" t="s">
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -3988,22 +8273,22 @@
         <v>66</v>
       </c>
       <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="D17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11">
         <v>8888</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="12.75">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
@@ -4027,20 +8312,16 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="14.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -4356,6 +8637,21 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" ht="14.25">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
